--- a/data/modelling/clustering/smartband/df_best_cluster_per_cust_need.xlsx
+++ b/data/modelling/clustering/smartband/df_best_cluster_per_cust_need.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,92 +446,81 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>pantalla</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>pantalla</t>
+          <t>diseño</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>diseño</t>
+          <t>bluetooth</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mejor calidad</t>
+          <t>Alta calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Calidad media</t>
+          <t>Baja calidad</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baja calidad</t>
+          <t>Media calidad</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -540,13 +529,10 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
